--- a/output_boron/boron_Intermediate_anderson_2024.xlsx
+++ b/output_boron/boron_Intermediate_anderson_2024.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
   <si>
     <t>NA</t>
   </si>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">ODP 1264_B_21_1_6_9</t>
+    <t xml:space="preserve">____6_9</t>
   </si>
   <si>
     <t xml:space="preserve">10.1029/2022PA004569</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_anderson_2024.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_anderson_2024.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">MC-ICPMS</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 1264_B_21_1_13_16</t>
+    <t xml:space="preserve">____13_16</t>
   </si>
   <si>
     <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2022</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 1264_B_21_1_20_23</t>
+    <t xml:space="preserve">____20_23</t>
   </si>
   <si>
     <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2023</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 1264_B_21_1_27_30</t>
+    <t xml:space="preserve">____27_30</t>
   </si>
   <si>
     <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2024</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">~180</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 1264_B_22_5_55_60</t>
+    <t xml:space="preserve">____55_60</t>
   </si>
   <si>
     <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2029</t>
@@ -1451,13 +1451,79 @@
     <t xml:space="preserve">~300</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 1264_B_24_5_20_24</t>
+    <t xml:space="preserve">____20_24</t>
   </si>
   <si>
     <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2030</t>
   </si>
   <si>
     <t xml:space="preserve">~350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">____6_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">____125_129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">____130_132.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciperoella angulisuturalis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212-250 µm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150-250 µm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">____60_64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">____91_95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drury, A. J., Liebrand, D., Westerhold, T., Beddow, H. M., Hodell, D. A., Rohlfs, N., Wilkens, R. H., Lyle, M., Bell, D. B., Kroon, D., Pälike, H., &amp; Lourens, L. J. (2021). Climate, cryosphere and carbon cycle controls on Southeast Atlantic orbital-scale carbonate deposition since the Oligocene (30–0&amp;thinsp;Ma). Climate of the Past, 17(5), 2091–2117. https://doi.org/10.5194/cp-17-2091-2037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~630</t>
   </si>
 </sst>
 </file>
@@ -1465,7 +1531,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1525,12 +1591,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1644,7 +1704,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1726,7 +1786,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2333,7 +2392,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2410,7 +2469,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2487,7 +2546,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2564,7 +2623,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2641,7 +2700,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2718,7 +2777,7 @@
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2795,7 +2854,7 @@
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2872,7 +2931,7 @@
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -2949,7 +3008,7 @@
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3026,7 +3085,7 @@
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3097,26 +3156,543 @@
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="E15" s="10"/>
-      <c r="U15" s="9"/>
+      <c r="A15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B15" t="s">
+        <v>241</v>
+      </c>
+      <c r="C15" t="s">
+        <v>242</v>
+      </c>
+      <c r="D15" t="s">
+        <v>243</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-28.533</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="H15" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="I15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L15" t="s">
+        <v>273</v>
+      </c>
+      <c r="M15" t="s">
+        <v>258</v>
+      </c>
+      <c r="N15" t="s">
+        <v>259</v>
+      </c>
+      <c r="O15" t="s">
+        <v>274</v>
+      </c>
+      <c r="P15" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.10525</v>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2</v>
+      </c>
+      <c r="W15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y15" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="U16" s="9"/>
+      <c r="A16" t="s">
+        <v>275</v>
+      </c>
+      <c r="B16" t="s">
+        <v>241</v>
+      </c>
+      <c r="C16" t="s">
+        <v>242</v>
+      </c>
+      <c r="D16" t="s">
+        <v>243</v>
+      </c>
+      <c r="E16" t="s">
+        <v>244</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-28.533</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="H16" t="n">
+        <v>25.572</v>
+      </c>
+      <c r="I16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L16" t="s">
+        <v>276</v>
+      </c>
+      <c r="M16" t="s">
+        <v>258</v>
+      </c>
+      <c r="N16" t="s">
+        <v>259</v>
+      </c>
+      <c r="O16" t="s">
+        <v>277</v>
+      </c>
+      <c r="P16" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.08975</v>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+      <c r="W16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y16" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="U17" s="9"/>
+      <c r="A17" t="s">
+        <v>278</v>
+      </c>
+      <c r="B17" t="s">
+        <v>241</v>
+      </c>
+      <c r="C17" t="s">
+        <v>242</v>
+      </c>
+      <c r="D17" t="s">
+        <v>243</v>
+      </c>
+      <c r="E17" t="s">
+        <v>244</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-28.533</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="H17" t="n">
+        <v>25.577</v>
+      </c>
+      <c r="I17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L17" t="s">
+        <v>279</v>
+      </c>
+      <c r="M17" t="s">
+        <v>258</v>
+      </c>
+      <c r="N17" t="s">
+        <v>259</v>
+      </c>
+      <c r="O17" t="s">
+        <v>280</v>
+      </c>
+      <c r="P17" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2</v>
+      </c>
+      <c r="W17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y17" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="U18" s="9"/>
+      <c r="A18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B18" t="s">
+        <v>241</v>
+      </c>
+      <c r="C18" t="s">
+        <v>242</v>
+      </c>
+      <c r="D18" t="s">
+        <v>243</v>
+      </c>
+      <c r="E18" t="s">
+        <v>244</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-28.533</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="H18" t="n">
+        <v>25.572</v>
+      </c>
+      <c r="I18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L18" t="s">
+        <v>281</v>
+      </c>
+      <c r="M18" t="s">
+        <v>282</v>
+      </c>
+      <c r="N18" t="s">
+        <v>283</v>
+      </c>
+      <c r="O18" t="s">
+        <v>284</v>
+      </c>
+      <c r="P18" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="U18" s="9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2</v>
+      </c>
+      <c r="W18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y18" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="U19" s="9"/>
+      <c r="A19" t="s">
+        <v>278</v>
+      </c>
+      <c r="B19" t="s">
+        <v>241</v>
+      </c>
+      <c r="C19" t="s">
+        <v>242</v>
+      </c>
+      <c r="D19" t="s">
+        <v>243</v>
+      </c>
+      <c r="E19" t="s">
+        <v>244</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-28.533</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="H19" t="n">
+        <v>25.577</v>
+      </c>
+      <c r="I19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L19" t="s">
+        <v>285</v>
+      </c>
+      <c r="M19" t="s">
+        <v>282</v>
+      </c>
+      <c r="N19" t="s">
+        <v>286</v>
+      </c>
+      <c r="O19" t="s">
+        <v>287</v>
+      </c>
+      <c r="P19" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.11375</v>
+      </c>
+      <c r="U19" s="9" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2</v>
+      </c>
+      <c r="W19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y19" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="U20" s="9"/>
+      <c r="A20" t="s">
+        <v>288</v>
+      </c>
+      <c r="B20" t="s">
+        <v>241</v>
+      </c>
+      <c r="C20" t="s">
+        <v>242</v>
+      </c>
+      <c r="D20" t="s">
+        <v>243</v>
+      </c>
+      <c r="E20" t="s">
+        <v>244</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-28.533</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="H20" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="I20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L20" t="s">
+        <v>289</v>
+      </c>
+      <c r="M20" t="s">
+        <v>282</v>
+      </c>
+      <c r="N20" t="s">
+        <v>286</v>
+      </c>
+      <c r="O20" t="s">
+        <v>290</v>
+      </c>
+      <c r="P20" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="U20" s="9" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
+      <c r="W20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y20" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="U21" s="9"/>
+      <c r="A21" t="s">
+        <v>291</v>
+      </c>
+      <c r="B21" t="s">
+        <v>241</v>
+      </c>
+      <c r="C21" t="s">
+        <v>242</v>
+      </c>
+      <c r="D21" t="s">
+        <v>243</v>
+      </c>
+      <c r="E21" t="s">
+        <v>244</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-28.533</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="H21" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="I21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L21" t="s">
+        <v>292</v>
+      </c>
+      <c r="M21" t="s">
+        <v>282</v>
+      </c>
+      <c r="N21" t="s">
+        <v>286</v>
+      </c>
+      <c r="O21" t="s">
+        <v>293</v>
+      </c>
+      <c r="P21" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.1165</v>
+      </c>
+      <c r="U21" s="9" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2</v>
+      </c>
+      <c r="W21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y21" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="U22" s="9"/>
@@ -3379,18 +3955,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
